--- a/Config/Item.xlsx
+++ b/Config/Item.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjects\zizouqi\Config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{017471CD-0B8D-4ED1-BE23-A2D94FFA8BB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE68B59C-B6AF-4EBC-AF94-2748CBEEE8D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21600" yWindow="-1770" windowWidth="21810" windowHeight="23430" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21600" yWindow="-60" windowWidth="21810" windowHeight="23430" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -148,7 +148,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="66">
   <si>
     <t>#</t>
   </si>
@@ -398,6 +398,10 @@
   </si>
   <si>
     <t>飞剑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>施法飞剑</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -753,7 +757,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="13.7265625" customWidth="1"/>
@@ -1038,144 +1042,132 @@
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
+      <c r="B11">
+        <v>10</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F11">
+        <v>2</v>
+      </c>
+      <c r="G11" s="1">
+        <v>4001</v>
+      </c>
+      <c r="L11">
+        <v>8</v>
+      </c>
+      <c r="M11">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="1"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B12">
-        <v>1001</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E12" s="2"/>
-      <c r="F12">
-        <v>1</v>
-      </c>
-      <c r="G12">
-        <v>4501</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K12" s="2"/>
-      <c r="L12">
-        <v>3</v>
-      </c>
-      <c r="M12">
-        <v>120</v>
-      </c>
+      <c r="D12" s="1"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B13">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>57</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="E13" s="2"/>
       <c r="F13">
         <v>1</v>
       </c>
       <c r="G13">
-        <v>4502</v>
+        <v>4501</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>34</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="K13" s="2"/>
       <c r="L13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M13">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B14">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F14">
         <v>1</v>
       </c>
       <c r="G14">
+        <v>4502</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="L14">
+        <v>4</v>
+      </c>
+      <c r="M14">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B15">
+        <v>1003</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15">
         <v>4503</v>
       </c>
-      <c r="J14" s="2" t="s">
+      <c r="J15" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="K14" s="2" t="s">
+      <c r="K15" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="L14">
+      <c r="L15">
         <v>5</v>
       </c>
-      <c r="M14">
+      <c r="M15">
         <v>123</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D15" s="1"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B16">
-        <v>2001</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="F16">
-        <v>2</v>
-      </c>
-      <c r="G16">
-        <v>4001</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="I16" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L16">
-        <v>1</v>
-      </c>
-      <c r="M16">
-        <v>200</v>
-      </c>
+      <c r="D16" s="1"/>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B17">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F17">
         <v>2</v>
@@ -1184,23 +1176,55 @@
         <v>4001</v>
       </c>
       <c r="H17" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L17">
+        <v>1</v>
+      </c>
+      <c r="M17">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B18">
+        <v>2002</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F18">
+        <v>2</v>
+      </c>
+      <c r="G18">
+        <v>4001</v>
+      </c>
+      <c r="H18" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="I17" s="6" t="s">
+      <c r="I18" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="J17" s="2" t="s">
+      <c r="J18" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="L17">
+      <c r="L18">
         <v>1001</v>
       </c>
-      <c r="M17">
+      <c r="M18">
         <v>300</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
         <v>62</v>
       </c>
     </row>

--- a/Config/Item.xlsx
+++ b/Config/Item.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjects\zizouqi\Config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE68B59C-B6AF-4EBC-AF94-2748CBEEE8D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13A4333E-3FC7-410F-B8B5-6EA721E03CFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21600" yWindow="-60" windowWidth="21810" windowHeight="23430" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21720" yWindow="-3600" windowWidth="21840" windowHeight="37920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -148,7 +148,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="69">
   <si>
     <t>#</t>
   </si>
@@ -402,6 +402,18 @@
   </si>
   <si>
     <t>施法飞剑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemDecs_Axes</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemDecs_Bullet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemDecs_Shield</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -908,7 +920,9 @@
       <c r="D5" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E5" s="2"/>
+      <c r="E5" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="F5">
         <v>1</v>
       </c>
@@ -938,7 +952,9 @@
       <c r="D6" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="E6" s="2"/>
+      <c r="E6" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F6">
         <v>1</v>
       </c>
@@ -962,7 +978,9 @@
         <v>63</v>
       </c>
       <c r="D7" s="1"/>
-      <c r="E7" s="2"/>
+      <c r="E7" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="F7">
         <v>1</v>
       </c>
@@ -979,6 +997,9 @@
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>62</v>
+      </c>
       <c r="B8">
         <v>7</v>
       </c>
@@ -1160,6 +1181,9 @@
       <c r="D16" s="1"/>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>62</v>
+      </c>
       <c r="B17">
         <v>2001</v>
       </c>
@@ -1192,6 +1216,9 @@
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>62</v>
+      </c>
       <c r="B18">
         <v>2002</v>
       </c>

--- a/Config/Item.xlsx
+++ b/Config/Item.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjects\zizouqi\Config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13A4333E-3FC7-410F-B8B5-6EA721E03CFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCCD512C-B0A4-44F5-8E60-3F34C01D4621}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-21720" yWindow="-3600" windowWidth="21840" windowHeight="37920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -112,34 +112,22 @@
           </rPr>
           <t xml:space="preserve">
 [InspectorName("当前血量")]
-Hp,
-[InspectorName("最大血量")]
-MaxHp,
-[InspectorName("当前蓝量")]
-Power,
-[InspectorName("最大蓝量")]
-[InspectorName("护盾")]
-HuDun,
-[InspectorName("攻击力")]
-AttackDamage,
-[InspectorName("法强")]
-AbilityPower,
-[InspectorName("普攻速")]
-AttackSpeed,
-[InspectorName("移速")]
-MovementSpeed,
-[InspectorName("护甲")]
-Armor,
-[InspectorName("魔抗")]
-MagicResist,
-[InspectorName("护甲穿透固定值")]
-ArmorPenetrationNum,
-[InspectorName("护甲穿透百分比")]
-ArmorPenetrationPercent,
-[InspectorName("法穿固定值")]
-MagicPenetrationNum,
-[InspectorName("法穿百分比")]
-MagicPenetrationPercent,</t>
+        Hp = 1,
+        [InspectorName("最大血量")]
+        MaxHp = 2,
+        [InspectorName("当前蓝量")]
+        Power = 3,
+        [InspectorName("最大蓝量")]
+        MaxPower = 4,
+        [InspectorName("护盾")]
+        HuDun = 5,
+        [InspectorName("护盾增益")]
+        HuDunBoost = 6,
+        [InspectorName("技能急速")]
+        CooldownReduce = 7,
+        [InspectorName("攻击力")]
+        AttackDamage = 8,
+</t>
         </r>
       </text>
     </comment>
@@ -148,7 +136,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="79">
   <si>
     <t>#</t>
   </si>
@@ -223,10 +211,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1,1;5,1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>合成材料</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -283,14 +267,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>9,40</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>9,30</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>AssetIDList</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -405,15 +381,66 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ItemDecs_Axes</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ItemDecs_Bullet</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ItemDecs_Shield</t>
+    <t>护甲板</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemName_ArmorPlate</t>
+  </si>
+  <si>
+    <t>ItemName_MoreFast</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemDesc_Axes</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemDesc_Bullet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemDesc_Shield</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemDesc_ArmorPlate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemDesc_MoreFast</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemDesc_FlySword</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemName_FlySword</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemDesc_FlySwordAnim</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemDesc_WhirlingAxe</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemDesc_ThornArmor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6,20;2,500</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemName_Shield</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemName_FlySwordAnim</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -769,7 +796,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="13.7265625" customWidth="1"/>
@@ -803,7 +830,7 @@
         <v>10</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>6</v>
@@ -812,22 +839,22 @@
         <v>8</v>
       </c>
       <c r="H2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I2" s="6" t="s">
         <v>36</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>39</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>17</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
@@ -851,10 +878,10 @@
         <v>3</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>18</v>
@@ -866,7 +893,7 @@
         <v>3</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
@@ -877,13 +904,13 @@
         <v>5</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>12</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>7</v>
@@ -892,22 +919,22 @@
         <v>9</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
@@ -918,9 +945,9 @@
         <v>13</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="E5" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>66</v>
       </c>
       <c r="F5">
@@ -933,7 +960,7 @@
         <v>2004</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="L5">
         <v>1</v>
@@ -950,9 +977,9 @@
         <v>14</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E6" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>67</v>
       </c>
       <c r="F6">
@@ -975,17 +1002,19 @@
         <v>3</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>68</v>
       </c>
       <c r="F7">
         <v>1</v>
       </c>
       <c r="G7" s="1">
-        <v>4003</v>
+        <v>4504</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" s="8"/>
@@ -997,236 +1026,242 @@
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>62</v>
-      </c>
       <c r="B8">
-        <v>7</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>42</v>
+        <v>4</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="E8" s="2"/>
-      <c r="F8">
-        <v>1</v>
+        <v>64</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>69</v>
       </c>
       <c r="G8" s="1">
-        <v>4000</v>
+        <v>4004</v>
       </c>
       <c r="H8" s="1"/>
       <c r="I8" s="8"/>
-      <c r="M8">
-        <v>50</v>
+      <c r="K8" s="2" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>59</v>
+      </c>
       <c r="B9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>61</v>
+        <v>39</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>52</v>
       </c>
       <c r="F9">
         <v>1</v>
       </c>
-      <c r="G9">
-        <v>4001</v>
-      </c>
-      <c r="L9">
-        <v>10002</v>
-      </c>
+      <c r="G9" s="1">
+        <v>4000</v>
+      </c>
+      <c r="H9" s="1"/>
+      <c r="I9" s="8"/>
       <c r="M9">
-        <v>20</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>64</v>
+        <v>58</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>70</v>
       </c>
       <c r="F10">
         <v>1</v>
       </c>
-      <c r="G10" s="1">
-        <v>4001</v>
+      <c r="G10">
+        <v>4508</v>
       </c>
       <c r="L10">
-        <v>7</v>
+        <v>10002</v>
       </c>
       <c r="M10">
-        <v>27</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B11">
+        <v>9</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11" s="1">
+        <v>4505</v>
+      </c>
+      <c r="L11">
+        <v>7</v>
+      </c>
+      <c r="M11">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B12">
         <v>10</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F11">
+      <c r="C12" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F12">
         <v>2</v>
       </c>
-      <c r="G11" s="1">
-        <v>4001</v>
-      </c>
-      <c r="L11">
+      <c r="G12" s="1">
+        <v>4506</v>
+      </c>
+      <c r="L12">
         <v>8</v>
       </c>
-      <c r="M11">
+      <c r="M12">
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="1"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B13">
-        <v>1001</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E13" s="2"/>
-      <c r="F13">
-        <v>1</v>
-      </c>
-      <c r="G13">
-        <v>4501</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K13" s="2"/>
-      <c r="L13">
-        <v>3</v>
-      </c>
-      <c r="M13">
-        <v>120</v>
-      </c>
+      <c r="D13" s="1"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B14">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>57</v>
+        <v>53</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>74</v>
       </c>
       <c r="F14">
         <v>1</v>
       </c>
       <c r="G14">
-        <v>4502</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>34</v>
-      </c>
+        <v>4501</v>
+      </c>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
       <c r="L14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M14">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B15">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>75</v>
       </c>
       <c r="F15">
         <v>1</v>
       </c>
       <c r="G15">
-        <v>4503</v>
+        <v>4502</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>35</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="K15" s="2"/>
       <c r="L15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M15">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D16" s="1"/>
+        <v>59</v>
+      </c>
+      <c r="B16">
+        <v>1003</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16">
+        <v>4503</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="K16" s="2"/>
+      <c r="L16">
+        <v>5</v>
+      </c>
+      <c r="M16">
+        <v>123</v>
+      </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B17">
-        <v>2001</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="F17">
-        <v>2</v>
-      </c>
-      <c r="G17">
-        <v>4001</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="I17" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L17">
-        <v>1</v>
-      </c>
-      <c r="M17">
-        <v>200</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="D17" s="1"/>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B18">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F18">
         <v>2</v>
@@ -1235,24 +1270,59 @@
         <v>4001</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="I18" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>43</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="L18">
-        <v>1001</v>
+        <v>1</v>
       </c>
       <c r="M18">
-        <v>300</v>
+        <v>200</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
+      </c>
+      <c r="B19">
+        <v>2002</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F19">
+        <v>2</v>
+      </c>
+      <c r="G19">
+        <v>4001</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="L19">
+        <v>1001</v>
+      </c>
+      <c r="M19">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
